--- a/Documents_after_matching.xlsx
+++ b/Documents_after_matching.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\AP\Accounts Payables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F33BCA69-645B-4FCD-B2AE-59DE89C6D480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F72A3D7-BD58-4A56-8D98-F867015A712A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9330" yWindow="3360" windowWidth="11505" windowHeight="7785" firstSheet="9" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3345" yWindow="3015" windowWidth="11505" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01 Purchase Orders" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'05 Credit Notes'!$A$1:$O$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'06 AP Reconciliation'!$A$1:$J$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'07 Bank Statement'!$A$1:$M$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'08 Tax Summary'!$A$1:$B$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'08 Tax Summary'!$A$1:$B$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'09 Three-Way Match'!$A$1:$H$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="247">
   <si>
     <t>PO Number</t>
   </si>
@@ -213,9 +213,6 @@
     <t>GRN-2026-05-003</t>
   </si>
   <si>
-    <t>Variance - investigate</t>
-  </si>
-  <si>
     <t>GRN-2026-05-004</t>
   </si>
   <si>
@@ -402,9 +399,6 @@
     <t>DN-PK-2026-05-001</t>
   </si>
   <si>
-    <t>Short delivery against PO/GRN</t>
-  </si>
-  <si>
     <t>DN-PK-2026-05-002</t>
   </si>
   <si>
@@ -414,9 +408,6 @@
     <t>DN-PK-2026-05-004</t>
   </si>
   <si>
-    <t>Damaged quantity accepted for debit adjustment</t>
-  </si>
-  <si>
     <t>Credit Note Number</t>
   </si>
   <si>
@@ -426,9 +417,6 @@
     <t>CN-SM-2026-05-001</t>
   </si>
   <si>
-    <t>Price adjustment agreed after invoice</t>
-  </si>
-  <si>
     <t>CN-SM-2026-05-002</t>
   </si>
   <si>
@@ -621,9 +609,6 @@
     <t>Tax / Reconciliation Item</t>
   </si>
   <si>
-    <t>Amount / Value</t>
-  </si>
-  <si>
     <t>Standard VAT rate used in training scenario</t>
   </si>
   <si>
@@ -733,17 +718,97 @@
   </si>
   <si>
     <t>All records are fictional training data and may not be represented as genuine business, bank, supplier, or tax records</t>
+  </si>
+  <si>
+    <t>Short delivery against PO/GRN verified</t>
+  </si>
+  <si>
+    <t>Damaged quantity accepted for debit adjustment after verification</t>
+  </si>
+  <si>
+    <t>Short delivery of 5 MT, is now corrected by Debit note DN-PK-2026-05-001</t>
+  </si>
+  <si>
+    <t>Short delivery of 8 MT, is now corrected by Debit note DN-PK-2026-05-002</t>
+  </si>
+  <si>
+    <t>5 MT damaged goods is corrected by Debit note DN-PK-2026-05-004</t>
+  </si>
+  <si>
+    <t>Short delivery of 10 MT is corrected by Debit note DN-PK-2026-05-003</t>
+  </si>
+  <si>
+    <t>Outstanding Balance</t>
+  </si>
+  <si>
+    <t>Paid through Bank</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Established roles are:</t>
+  </si>
+  <si>
+    <t>Peter Ke. Ltd: Buyer, responsible for checking deliveries, verifying invoices, issuing debit notes where necessary, and reconciling amounts payable.</t>
+  </si>
+  <si>
+    <t>Sacho Mills: Supplier, responsible for supplying the goods and issuing invoices and any applicable credit notes.</t>
+  </si>
+  <si>
+    <t>Debit notes (DN): Issued by Peter Ke. Ltd to Sacho Mills to claim a reduction for issues such as shortages or damage.</t>
+  </si>
+  <si>
+    <t>Credit notes (CN): Issued by Sacho Mills to Peter Ke. Ltd to acknowledge reductions in amounts previously invoiced.</t>
+  </si>
+  <si>
+    <t>For Peter Ke. Ltd (buyer) purchasing goods from Sacho Mills (supplier), both debit notes and credit notes are considered against the Tax Invoice to determine the correct amount payable.</t>
+  </si>
+  <si>
+    <t>Peter Ke. Ltd are carrying out as the buyer</t>
+  </si>
+  <si>
+    <t>Price adjustment agreed after acknowledgement of invoice reduction</t>
+  </si>
+  <si>
+    <t>Sacho Mills issues a Tax Invoice for $433,333.08, Peter Ke. Ltd issues a valid Debit Note for $7325.5, and Sacho Mills issues a Credit Note for $1252.5:</t>
+  </si>
+  <si>
+    <t>Variance - investigate 5 MT</t>
+  </si>
+  <si>
+    <t>Variance - investigate 10 MT</t>
+  </si>
+  <si>
+    <t>Variance - investigate 8 MT</t>
+  </si>
+  <si>
+    <t>Damaged quantity 5 MT</t>
+  </si>
+  <si>
+    <t>433.333.08-7325.5-1252.8=424,754.88</t>
+  </si>
+  <si>
+    <t>Amount / Value($)</t>
+  </si>
+  <si>
+    <t>"Peter Ke.Ltd is a buyer and has only one supplier, Sacho Mills. This flips how Debit and Credit notes are handled here."</t>
+  </si>
+  <si>
+    <t>Adjusted Payable = Gross Invoice - Debit Note - Credit Note</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -773,6 +838,28 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -810,11 +897,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -822,11 +910,24 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -2027,7 +2128,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -2036,34 +2137,34 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="B3" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B4" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -2084,42 +2185,89 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B7" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B8" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="B9" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B10" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B11" t="s">
-        <v>225</v>
+        <v>220</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="8"/>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="10"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="10" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="10"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="10" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="10"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="10" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -2295,12 +2443,12 @@
         <v>48</v>
       </c>
       <c r="L4" t="s">
-        <v>52</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B5" s="2">
         <v>46147</v>
@@ -2338,7 +2486,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B6" s="2">
         <v>46149</v>
@@ -2376,7 +2524,7 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B7" s="2">
         <v>46150</v>
@@ -2414,7 +2562,7 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B8" s="2">
         <v>46152</v>
@@ -2452,7 +2600,7 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B9" s="2">
         <v>46153</v>
@@ -2479,18 +2627,18 @@
         <v>-8</v>
       </c>
       <c r="J9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K9" t="s">
         <v>48</v>
       </c>
       <c r="L9" t="s">
-        <v>52</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B10" s="2">
         <v>46155</v>
@@ -2528,7 +2676,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B11" s="2">
         <v>46156</v>
@@ -2561,12 +2709,12 @@
         <v>48</v>
       </c>
       <c r="L11" t="s">
-        <v>49</v>
+        <v>242</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B12" s="2">
         <v>46158</v>
@@ -2604,7 +2752,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B13" s="2">
         <v>46159</v>
@@ -2642,7 +2790,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B14" s="2">
         <v>46161</v>
@@ -2669,18 +2817,18 @@
         <v>-10</v>
       </c>
       <c r="J14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K14" t="s">
         <v>48</v>
       </c>
       <c r="L14" t="s">
-        <v>52</v>
+        <v>240</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B15" s="2">
         <v>46162</v>
@@ -2718,7 +2866,7 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B16" s="2">
         <v>46164</v>
@@ -2756,7 +2904,7 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B17" s="2">
         <v>46165</v>
@@ -2794,7 +2942,7 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B18" s="2">
         <v>46167</v>
@@ -2832,7 +2980,7 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B19" s="2">
         <v>46168</v>
@@ -2870,7 +3018,7 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B20" s="2">
         <v>46170</v>
@@ -2908,7 +3056,7 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B21" s="2">
         <v>46172</v>
@@ -2952,7 +3100,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:R22"/>
+  <dimension ref="A1:R25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -2976,10 +3124,10 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>3</v>
@@ -2988,10 +3136,10 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>74</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>0</v>
@@ -3003,7 +3151,7 @@
         <v>4</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>6</v>
@@ -3012,27 +3160,27 @@
         <v>7</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="O1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B2" s="2">
         <v>46143</v>
@@ -3044,10 +3192,10 @@
         <v>14</v>
       </c>
       <c r="E2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F2" t="s">
         <v>82</v>
-      </c>
-      <c r="F2" t="s">
-        <v>83</v>
       </c>
       <c r="G2" t="s">
         <v>13</v>
@@ -3080,15 +3228,15 @@
         <v>10208</v>
       </c>
       <c r="Q2" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="R2" t="s">
         <v>84</v>
-      </c>
-      <c r="R2" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B3" s="2">
         <v>46144</v>
@@ -3100,10 +3248,10 @@
         <v>14</v>
       </c>
       <c r="E3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F3" t="s">
         <v>82</v>
-      </c>
-      <c r="F3" t="s">
-        <v>83</v>
       </c>
       <c r="G3" t="s">
         <v>19</v>
@@ -3136,15 +3284,15 @@
         <v>13717</v>
       </c>
       <c r="Q3" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="R3" t="s">
         <v>84</v>
-      </c>
-      <c r="R3" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B4" s="2">
         <v>46146</v>
@@ -3156,10 +3304,10 @@
         <v>14</v>
       </c>
       <c r="E4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F4" t="s">
         <v>82</v>
-      </c>
-      <c r="F4" t="s">
-        <v>83</v>
       </c>
       <c r="G4" t="s">
         <v>20</v>
@@ -3192,15 +3340,15 @@
         <v>16965</v>
       </c>
       <c r="Q4" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="R4" t="s">
         <v>84</v>
-      </c>
-      <c r="R4" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B5" s="2">
         <v>46147</v>
@@ -3212,16 +3360,16 @@
         <v>14</v>
       </c>
       <c r="E5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F5" t="s">
         <v>82</v>
-      </c>
-      <c r="F5" t="s">
-        <v>83</v>
       </c>
       <c r="G5" t="s">
         <v>21</v>
       </c>
       <c r="H5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I5" t="s">
         <v>16</v>
@@ -3248,15 +3396,15 @@
         <v>20706</v>
       </c>
       <c r="Q5" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="R5" t="s">
         <v>84</v>
-      </c>
-      <c r="R5" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B6" s="2">
         <v>46149</v>
@@ -3268,16 +3416,16 @@
         <v>14</v>
       </c>
       <c r="E6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F6" t="s">
         <v>82</v>
-      </c>
-      <c r="F6" t="s">
-        <v>83</v>
       </c>
       <c r="G6" t="s">
         <v>22</v>
       </c>
       <c r="H6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I6" t="s">
         <v>16</v>
@@ -3304,15 +3452,15 @@
         <v>24023.599999999999</v>
       </c>
       <c r="Q6" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="R6" t="s">
         <v>84</v>
-      </c>
-      <c r="R6" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B7" s="2">
         <v>46150</v>
@@ -3324,16 +3472,16 @@
         <v>14</v>
       </c>
       <c r="E7" t="s">
+        <v>81</v>
+      </c>
+      <c r="F7" t="s">
         <v>82</v>
-      </c>
-      <c r="F7" t="s">
-        <v>83</v>
       </c>
       <c r="G7" t="s">
         <v>23</v>
       </c>
       <c r="H7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I7" t="s">
         <v>16</v>
@@ -3360,15 +3508,15 @@
         <v>27051.200000000001</v>
       </c>
       <c r="Q7" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="R7" t="s">
         <v>84</v>
-      </c>
-      <c r="R7" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B8" s="2">
         <v>46152</v>
@@ -3380,16 +3528,16 @@
         <v>14</v>
       </c>
       <c r="E8" t="s">
+        <v>81</v>
+      </c>
+      <c r="F8" t="s">
         <v>82</v>
-      </c>
-      <c r="F8" t="s">
-        <v>83</v>
       </c>
       <c r="G8" t="s">
         <v>24</v>
       </c>
       <c r="H8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I8" t="s">
         <v>16</v>
@@ -3416,15 +3564,15 @@
         <v>31900</v>
       </c>
       <c r="Q8" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="R8" t="s">
         <v>84</v>
-      </c>
-      <c r="R8" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B9" s="2">
         <v>46153</v>
@@ -3436,16 +3584,16 @@
         <v>14</v>
       </c>
       <c r="E9" t="s">
+        <v>81</v>
+      </c>
+      <c r="F9" t="s">
         <v>82</v>
-      </c>
-      <c r="F9" t="s">
-        <v>83</v>
       </c>
       <c r="G9" t="s">
         <v>25</v>
       </c>
       <c r="H9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I9" t="s">
         <v>16</v>
@@ -3472,15 +3620,15 @@
         <v>13873.6</v>
       </c>
       <c r="Q9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="R9" t="s">
         <v>84</v>
-      </c>
-      <c r="R9" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B10" s="2">
         <v>46155</v>
@@ -3492,16 +3640,16 @@
         <v>14</v>
       </c>
       <c r="E10" t="s">
+        <v>81</v>
+      </c>
+      <c r="F10" t="s">
         <v>82</v>
-      </c>
-      <c r="F10" t="s">
-        <v>83</v>
       </c>
       <c r="G10" t="s">
         <v>26</v>
       </c>
       <c r="H10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I10" t="s">
         <v>16</v>
@@ -3528,15 +3676,15 @@
         <v>18792</v>
       </c>
       <c r="Q10" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="R10" t="s">
         <v>84</v>
-      </c>
-      <c r="R10" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B11" s="2">
         <v>46156</v>
@@ -3548,16 +3696,16 @@
         <v>14</v>
       </c>
       <c r="E11" t="s">
+        <v>81</v>
+      </c>
+      <c r="F11" t="s">
         <v>82</v>
-      </c>
-      <c r="F11" t="s">
-        <v>83</v>
       </c>
       <c r="G11" t="s">
         <v>27</v>
       </c>
       <c r="H11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I11" t="s">
         <v>16</v>
@@ -3584,15 +3732,15 @@
         <v>22341.599999999999</v>
       </c>
       <c r="Q11" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="R11" t="s">
         <v>84</v>
-      </c>
-      <c r="R11" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B12" s="2">
         <v>46158</v>
@@ -3604,16 +3752,16 @@
         <v>14</v>
       </c>
       <c r="E12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F12" t="s">
         <v>82</v>
-      </c>
-      <c r="F12" t="s">
-        <v>83</v>
       </c>
       <c r="G12" t="s">
         <v>28</v>
       </c>
       <c r="H12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I12" t="s">
         <v>16</v>
@@ -3640,15 +3788,15 @@
         <v>27039.599999999999</v>
       </c>
       <c r="Q12" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="R12" t="s">
         <v>84</v>
-      </c>
-      <c r="R12" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B13" s="2">
         <v>46159</v>
@@ -3660,16 +3808,16 @@
         <v>14</v>
       </c>
       <c r="E13" t="s">
+        <v>81</v>
+      </c>
+      <c r="F13" t="s">
         <v>82</v>
-      </c>
-      <c r="F13" t="s">
-        <v>83</v>
       </c>
       <c r="G13" t="s">
         <v>29</v>
       </c>
       <c r="H13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I13" t="s">
         <v>16</v>
@@ -3696,15 +3844,15 @@
         <v>30484.799999999999</v>
       </c>
       <c r="Q13" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="R13" t="s">
         <v>84</v>
-      </c>
-      <c r="R13" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B14" s="2">
         <v>46161</v>
@@ -3716,16 +3864,16 @@
         <v>14</v>
       </c>
       <c r="E14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F14" t="s">
         <v>82</v>
-      </c>
-      <c r="F14" t="s">
-        <v>83</v>
       </c>
       <c r="G14" t="s">
         <v>30</v>
       </c>
       <c r="H14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I14" t="s">
         <v>16</v>
@@ -3752,15 +3900,15 @@
         <v>14546.4</v>
       </c>
       <c r="Q14" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="R14" t="s">
         <v>84</v>
-      </c>
-      <c r="R14" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B15" s="2">
         <v>46162</v>
@@ -3772,16 +3920,16 @@
         <v>14</v>
       </c>
       <c r="E15" t="s">
+        <v>81</v>
+      </c>
+      <c r="F15" t="s">
         <v>82</v>
-      </c>
-      <c r="F15" t="s">
-        <v>83</v>
       </c>
       <c r="G15" t="s">
         <v>31</v>
       </c>
       <c r="H15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I15" t="s">
         <v>16</v>
@@ -3808,15 +3956,15 @@
         <v>20137.599999999999</v>
       </c>
       <c r="Q15" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="R15" t="s">
         <v>84</v>
-      </c>
-      <c r="R15" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B16" s="2">
         <v>46164</v>
@@ -3828,16 +3976,16 @@
         <v>14</v>
       </c>
       <c r="E16" t="s">
+        <v>81</v>
+      </c>
+      <c r="F16" t="s">
         <v>82</v>
-      </c>
-      <c r="F16" t="s">
-        <v>83</v>
       </c>
       <c r="G16" t="s">
         <v>32</v>
       </c>
       <c r="H16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I16" t="s">
         <v>16</v>
@@ -3864,15 +4012,15 @@
         <v>25636</v>
       </c>
       <c r="Q16" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="R16" t="s">
         <v>84</v>
-      </c>
-      <c r="R16" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B17" s="2">
         <v>46165</v>
@@ -3884,16 +4032,16 @@
         <v>14</v>
       </c>
       <c r="E17" t="s">
+        <v>81</v>
+      </c>
+      <c r="F17" t="s">
         <v>82</v>
-      </c>
-      <c r="F17" t="s">
-        <v>83</v>
       </c>
       <c r="G17" t="s">
         <v>33</v>
       </c>
       <c r="H17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I17" t="s">
         <v>16</v>
@@ -3920,15 +4068,15 @@
         <v>28414.2</v>
       </c>
       <c r="Q17" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="R17" t="s">
         <v>84</v>
-      </c>
-      <c r="R17" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B18" s="2">
         <v>46167</v>
@@ -3940,16 +4088,16 @@
         <v>14</v>
       </c>
       <c r="E18" t="s">
+        <v>81</v>
+      </c>
+      <c r="F18" t="s">
         <v>82</v>
-      </c>
-      <c r="F18" t="s">
-        <v>83</v>
       </c>
       <c r="G18" t="s">
         <v>34</v>
       </c>
       <c r="H18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I18" t="s">
         <v>16</v>
@@ -3976,15 +4124,15 @@
         <v>32874.400000000001</v>
       </c>
       <c r="Q18" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="R18" t="s">
         <v>84</v>
-      </c>
-      <c r="R18" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B19" s="2">
         <v>46168</v>
@@ -3996,16 +4144,16 @@
         <v>14</v>
       </c>
       <c r="E19" t="s">
+        <v>81</v>
+      </c>
+      <c r="F19" t="s">
         <v>82</v>
-      </c>
-      <c r="F19" t="s">
-        <v>83</v>
       </c>
       <c r="G19" t="s">
         <v>35</v>
       </c>
       <c r="H19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I19" t="s">
         <v>16</v>
@@ -4032,15 +4180,15 @@
         <v>13456</v>
       </c>
       <c r="Q19" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="R19" t="s">
         <v>84</v>
-      </c>
-      <c r="R19" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B20" s="2">
         <v>46170</v>
@@ -4052,16 +4200,16 @@
         <v>14</v>
       </c>
       <c r="E20" t="s">
+        <v>81</v>
+      </c>
+      <c r="F20" t="s">
         <v>82</v>
-      </c>
-      <c r="F20" t="s">
-        <v>83</v>
       </c>
       <c r="G20" t="s">
         <v>36</v>
       </c>
       <c r="H20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I20" t="s">
         <v>16</v>
@@ -4088,15 +4236,15 @@
         <v>18708.48</v>
       </c>
       <c r="Q20" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="R20" t="s">
         <v>84</v>
-      </c>
-      <c r="R20" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B21" s="2">
         <v>46172</v>
@@ -4108,16 +4256,16 @@
         <v>14</v>
       </c>
       <c r="E21" t="s">
+        <v>81</v>
+      </c>
+      <c r="F21" t="s">
         <v>82</v>
-      </c>
-      <c r="F21" t="s">
-        <v>83</v>
       </c>
       <c r="G21" t="s">
         <v>37</v>
       </c>
       <c r="H21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I21" t="s">
         <v>16</v>
@@ -4144,10 +4292,10 @@
         <v>22457.599999999999</v>
       </c>
       <c r="Q21" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="R21" t="s">
         <v>84</v>
-      </c>
-      <c r="R21" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
@@ -4159,6 +4307,16 @@
         <f>SUM(O2:O21)</f>
         <v>59770.079999999994</v>
       </c>
+      <c r="P22" s="3">
+        <f>SUM(P2:P21)</f>
+        <v>433333.07999999996</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="N25" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:R21" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
@@ -4188,16 +4346,16 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>108</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -4206,36 +4364,36 @@
         <v>38</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B2" s="2">
         <v>46146</v>
@@ -4253,7 +4411,7 @@
         <v>51</v>
       </c>
       <c r="G2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H2" t="s">
         <v>16</v>
@@ -4277,12 +4435,12 @@
         <v>1305</v>
       </c>
       <c r="O2" t="s">
-        <v>115</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B3" s="2">
         <v>46153</v>
@@ -4297,10 +4455,10 @@
         <v>25</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H3" t="s">
         <v>16</v>
@@ -4324,12 +4482,12 @@
         <v>2134.4</v>
       </c>
       <c r="O3" t="s">
-        <v>115</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B4" s="2">
         <v>46161</v>
@@ -4344,10 +4502,10 @@
         <v>30</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H4" t="s">
         <v>16</v>
@@ -4371,12 +4529,12 @@
         <v>2644.8</v>
       </c>
       <c r="O4" t="s">
-        <v>115</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B5" s="2">
         <v>46156</v>
@@ -4391,10 +4549,10 @@
         <v>27</v>
       </c>
       <c r="F5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H5" t="s">
         <v>16</v>
@@ -4418,7 +4576,7 @@
         <v>1241.2</v>
       </c>
       <c r="O5" t="s">
-        <v>119</v>
+        <v>222</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
@@ -4463,16 +4621,16 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>108</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -4481,36 +4639,36 @@
         <v>38</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B2" s="2">
         <v>46149</v>
@@ -4525,10 +4683,10 @@
         <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H2" t="s">
         <v>16</v>
@@ -4552,12 +4710,12 @@
         <v>758.64</v>
       </c>
       <c r="O2" t="s">
-        <v>123</v>
+        <v>237</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B3" s="2">
         <v>46165</v>
@@ -4572,10 +4730,10 @@
         <v>33</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H3" t="s">
         <v>16</v>
@@ -4599,13 +4757,17 @@
         <v>494.16</v>
       </c>
       <c r="O3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="M4" s="3">
         <f>SUM(M2:M3)</f>
         <v>172.8</v>
+      </c>
+      <c r="N4" s="3">
+        <f>SUM(N2:N3)</f>
+        <v>1252.8</v>
       </c>
     </row>
   </sheetData>
@@ -4616,7 +4778,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -4632,10 +4794,10 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -4644,27 +4806,27 @@
         <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="H1" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B2" s="2">
         <v>46143</v>
@@ -4696,7 +4858,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B3" s="2">
         <v>46144</v>
@@ -4728,7 +4890,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B4" s="2">
         <v>46146</v>
@@ -4746,7 +4908,7 @@
         <v>2520</v>
       </c>
       <c r="G4" s="3">
-        <v>18270</v>
+        <v>16965</v>
       </c>
       <c r="H4" s="3">
         <v>1305</v>
@@ -4755,12 +4917,12 @@
         <v>0</v>
       </c>
       <c r="J4" s="3">
-        <v>19575</v>
+        <v>15660</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B5" s="2">
         <v>46147</v>
@@ -4769,7 +4931,7 @@
         <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E5" s="3">
         <v>17850</v>
@@ -4792,7 +4954,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B6" s="2">
         <v>46149</v>
@@ -4801,7 +4963,7 @@
         <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E6" s="3">
         <v>20710</v>
@@ -4825,7 +4987,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B7" s="2">
         <v>46150</v>
@@ -4834,7 +4996,7 @@
         <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E7" s="3">
         <v>23320</v>
@@ -4857,7 +5019,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B8" s="2">
         <v>46152</v>
@@ -4866,7 +5028,7 @@
         <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E8" s="3">
         <v>27500</v>
@@ -4889,7 +5051,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B9" s="2">
         <v>46153</v>
@@ -4898,16 +5060,17 @@
         <v>25</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E9" s="4">
         <v>13800</v>
       </c>
       <c r="F9" s="3">
+        <f>0.16*E9</f>
         <v>2208</v>
       </c>
       <c r="G9" s="3">
-        <v>16008</v>
+        <v>13873.6</v>
       </c>
       <c r="H9" s="3">
         <v>2134.4</v>
@@ -4916,12 +5079,12 @@
         <v>0</v>
       </c>
       <c r="J9" s="3">
-        <v>18142.400000000001</v>
+        <v>11739.2</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B10" s="2">
         <v>46155</v>
@@ -4930,7 +5093,7 @@
         <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E10" s="3">
         <v>16200</v>
@@ -4953,7 +5116,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B11" s="2">
         <v>46156</v>
@@ -4962,7 +5125,7 @@
         <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E11" s="4">
         <v>19260</v>
@@ -4980,12 +5143,12 @@
         <v>0</v>
       </c>
       <c r="J11" s="3">
-        <v>23582.799999999999</v>
+        <v>21100.399999999998</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B12" s="2">
         <v>46158</v>
@@ -4994,7 +5157,7 @@
         <v>28</v>
       </c>
       <c r="D12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E12" s="3">
         <v>23310</v>
@@ -5017,7 +5180,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B13" s="2">
         <v>46159</v>
@@ -5026,7 +5189,7 @@
         <v>29</v>
       </c>
       <c r="D13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E13" s="3">
         <v>26280</v>
@@ -5049,7 +5212,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B14" s="2">
         <v>46161</v>
@@ -5058,7 +5221,7 @@
         <v>30</v>
       </c>
       <c r="D14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E14" s="4">
         <v>14820</v>
@@ -5067,7 +5230,7 @@
         <v>2371.1999999999998</v>
       </c>
       <c r="G14" s="3">
-        <v>17191.2</v>
+        <v>14546.4</v>
       </c>
       <c r="H14" s="3">
         <v>2644.8</v>
@@ -5076,12 +5239,12 @@
         <v>0</v>
       </c>
       <c r="J14" s="3">
-        <v>19836</v>
+        <v>11901.6</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B15" s="2">
         <v>46162</v>
@@ -5090,7 +5253,7 @@
         <v>31</v>
       </c>
       <c r="D15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E15" s="3">
         <v>17360</v>
@@ -5113,7 +5276,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B16" s="2">
         <v>46164</v>
@@ -5122,7 +5285,7 @@
         <v>32</v>
       </c>
       <c r="D16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E16" s="3">
         <v>22100</v>
@@ -5145,7 +5308,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B17" s="2">
         <v>46165</v>
@@ -5154,7 +5317,7 @@
         <v>33</v>
       </c>
       <c r="D17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E17" s="3">
         <v>24495</v>
@@ -5178,7 +5341,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B18" s="2">
         <v>46167</v>
@@ -5187,7 +5350,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E18" s="3">
         <v>28340</v>
@@ -5210,7 +5373,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B19" s="2">
         <v>46168</v>
@@ -5219,7 +5382,7 @@
         <v>35</v>
       </c>
       <c r="D19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E19" s="3">
         <v>11600</v>
@@ -5242,7 +5405,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B20" s="2">
         <v>46170</v>
@@ -5251,7 +5414,7 @@
         <v>36</v>
       </c>
       <c r="D20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E20" s="3">
         <v>16128</v>
@@ -5274,7 +5437,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B21" s="2">
         <v>46172</v>
@@ -5283,7 +5446,7 @@
         <v>37</v>
       </c>
       <c r="D21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E21" s="3">
         <v>19360</v>
@@ -5306,33 +5469,40 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="E22" s="3">
-        <f>SUM(E2:E21)</f>
+        <f t="shared" ref="E22:J22" si="0">SUM(E2:E21)</f>
         <v>378808</v>
       </c>
       <c r="F22" s="3">
-        <f>SUM(F2:F21)</f>
+        <f t="shared" si="0"/>
         <v>60609.279999999992</v>
       </c>
       <c r="G22" s="3">
-        <f>SUM(G2:G21)</f>
-        <v>439417.27999999997</v>
+        <f t="shared" si="0"/>
+        <v>433333.07999999996</v>
       </c>
       <c r="H22" s="3">
-        <f>SUM(H2:H21)</f>
+        <f t="shared" si="0"/>
         <v>7325.4000000000005</v>
       </c>
       <c r="I22" s="3">
-        <f>SUM(I2:I21)</f>
+        <f t="shared" si="0"/>
         <v>1252.8</v>
       </c>
       <c r="J22" s="3">
-        <f>SUM(J2:J21)</f>
-        <v>445489.87999999989</v>
+        <f t="shared" si="0"/>
+        <v>424754.87999999989</v>
       </c>
       <c r="K22" s="3"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="J23" s="3"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J25" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:J21" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
@@ -5343,7 +5513,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -5362,22 +5532,22 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>133</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>0</v>
@@ -5386,39 +5556,39 @@
         <v>38</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B2" s="2">
         <v>46143</v>
       </c>
       <c r="C2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G2" t="s">
         <v>13</v>
@@ -5439,27 +5609,27 @@
         <v>139792</v>
       </c>
       <c r="M2" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B3" s="2">
         <v>46144</v>
       </c>
       <c r="C3" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E3" t="s">
         <v>141</v>
       </c>
-      <c r="E3" t="s">
-        <v>145</v>
-      </c>
       <c r="F3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G3" t="s">
         <v>19</v>
@@ -5480,27 +5650,27 @@
         <v>126075</v>
       </c>
       <c r="M3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B4" s="2">
         <v>46146</v>
       </c>
       <c r="C4" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D4" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E4" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G4" t="s">
         <v>20</v>
@@ -5521,33 +5691,33 @@
         <v>110415</v>
       </c>
       <c r="M4" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B5" s="2">
         <v>46147</v>
       </c>
       <c r="C5" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D5" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E5" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="F5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G5" t="s">
         <v>21</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I5" s="3">
         <v>20706</v>
@@ -5562,24 +5732,24 @@
         <v>89709</v>
       </c>
       <c r="M5" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B6" s="2">
         <v>46147</v>
       </c>
       <c r="C6" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D6" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E6" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3">
@@ -5595,33 +5765,33 @@
         <v>108209</v>
       </c>
       <c r="M6" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B7" s="2">
         <v>46149</v>
       </c>
       <c r="C7" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D7" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E7" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="F7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G7" t="s">
         <v>22</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I7" s="3">
         <v>23264.959999999999</v>
@@ -5636,33 +5806,33 @@
         <v>84944.040000000008</v>
       </c>
       <c r="M7" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B8" s="2">
         <v>46150</v>
       </c>
       <c r="C8" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D8" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E8" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="F8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G8" t="s">
         <v>23</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I8" s="3">
         <v>27051.200000000001</v>
@@ -5677,33 +5847,33 @@
         <v>57892.84</v>
       </c>
       <c r="M8" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B9" s="2">
         <v>46152</v>
       </c>
       <c r="C9" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D9" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E9" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G9" t="s">
         <v>24</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I9" s="3">
         <v>31900</v>
@@ -5718,33 +5888,33 @@
         <v>25992.84</v>
       </c>
       <c r="M9" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B10" s="2">
         <v>46153</v>
       </c>
       <c r="C10" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D10" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E10" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G10" t="s">
         <v>25</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I10" s="3">
         <v>11739.2</v>
@@ -5759,33 +5929,33 @@
         <v>14253.639999999979</v>
       </c>
       <c r="M10" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B11" s="2">
         <v>46155</v>
       </c>
       <c r="C11" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D11" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E11" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G11" t="s">
         <v>26</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I11" s="3">
         <v>18792</v>
@@ -5800,33 +5970,33 @@
         <v>-4538.3600000000151</v>
       </c>
       <c r="M11" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B12" s="2">
         <v>46156</v>
       </c>
       <c r="C12" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D12" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E12" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G12" t="s">
         <v>27</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I12" s="3">
         <v>21100.400000000001</v>
@@ -5841,33 +6011,33 @@
         <v>-25638.760000000009</v>
       </c>
       <c r="M12" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B13" s="2">
         <v>46158</v>
       </c>
       <c r="C13" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D13" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E13" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="F13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G13" t="s">
         <v>28</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I13" s="3">
         <v>27039.599999999999</v>
@@ -5882,33 +6052,33 @@
         <v>-52678.360000000022</v>
       </c>
       <c r="M13" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B14" s="2">
         <v>46159</v>
       </c>
       <c r="C14" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D14" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E14" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G14" t="s">
         <v>29</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I14" s="3">
         <v>30484.799999999999</v>
@@ -5923,24 +6093,24 @@
         <v>-83163.16</v>
       </c>
       <c r="M14" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B15" s="2">
         <v>46159</v>
       </c>
       <c r="C15" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D15" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E15" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3">
@@ -5956,33 +6126,33 @@
         <v>-61163.16</v>
       </c>
       <c r="M15" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B16" s="2">
         <v>46161</v>
       </c>
       <c r="C16" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D16" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E16" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="F16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G16" t="s">
         <v>30</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I16" s="3">
         <v>11901.6</v>
@@ -5997,33 +6167,33 @@
         <v>-73064.760000000009</v>
       </c>
       <c r="M16" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B17" s="2">
         <v>46162</v>
       </c>
       <c r="C17" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D17" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E17" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F17" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G17" t="s">
         <v>31</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I17" s="3">
         <v>20137.599999999999</v>
@@ -6038,33 +6208,33 @@
         <v>-93202.360000000015</v>
       </c>
       <c r="M17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B18" s="2">
         <v>46164</v>
       </c>
       <c r="C18" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D18" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E18" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F18" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G18" t="s">
         <v>32</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I18" s="3">
         <v>25636</v>
@@ -6079,33 +6249,33 @@
         <v>-118838.36</v>
       </c>
       <c r="M18" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B19" s="2">
         <v>46165</v>
       </c>
       <c r="C19" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D19" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E19" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F19" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G19" t="s">
         <v>33</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I19" s="3">
         <v>27920.04</v>
@@ -6120,33 +6290,33 @@
         <v>-146758.39999999999</v>
       </c>
       <c r="M19" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B20" s="2">
         <v>46167</v>
       </c>
       <c r="C20" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D20" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E20" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="F20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G20" t="s">
         <v>34</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I20" s="3">
         <v>32874.400000000001</v>
@@ -6161,33 +6331,33 @@
         <v>-179632.8</v>
       </c>
       <c r="M20" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B21" s="2">
         <v>46168</v>
       </c>
       <c r="C21" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D21" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E21" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="F21" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G21" t="s">
         <v>35</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I21" s="3">
         <v>13456</v>
@@ -6202,33 +6372,33 @@
         <v>-193088.8</v>
       </c>
       <c r="M21" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B22" s="2">
         <v>46170</v>
       </c>
       <c r="C22" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D22" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E22" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="F22" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G22" t="s">
         <v>36</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I22" s="3">
         <v>18708.48</v>
@@ -6243,24 +6413,24 @@
         <v>-211797.28</v>
       </c>
       <c r="M22" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B23" s="2">
         <v>46170</v>
       </c>
       <c r="C23" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D23" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E23" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3">
@@ -6276,33 +6446,33 @@
         <v>-196797.28</v>
       </c>
       <c r="M23" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B24" s="2">
         <v>46172</v>
       </c>
       <c r="C24" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D24" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E24" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G24" t="s">
         <v>37</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I24" s="3">
         <v>22457.599999999999</v>
@@ -6317,7 +6487,13 @@
         <v>-219254.87999999989</v>
       </c>
       <c r="M24" t="s">
-        <v>143</v>
+        <v>139</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I25" s="3">
+        <f>SUM(I2:I24)</f>
+        <v>424754.87999999989</v>
       </c>
     </row>
   </sheetData>
@@ -6328,112 +6504,167 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="32" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+      <c r="C2" s="5"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B3" s="5">
         <v>373563</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C3" s="5"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B4" s="5">
         <v>59770.080000000002</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C4" s="5"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="B5" s="5">
-        <v>1010.4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7325.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B6" s="5">
-        <v>172.8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1252.8</v>
+      </c>
+      <c r="C6" s="5"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="B7" s="5">
         <v>60609.279999999999</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C7" s="5"/>
+      <c r="D7" s="7"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>191</v>
+      </c>
+      <c r="B8" s="5">
+        <v>433333.07999999996</v>
+      </c>
+      <c r="C8" s="5"/>
+      <c r="D8" s="6"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>192</v>
+      </c>
+      <c r="B9" s="5">
+        <v>424754.88</v>
+      </c>
+      <c r="C9" s="5"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>228</v>
+      </c>
+      <c r="B10" s="5">
+        <v>424754.88</v>
+      </c>
+      <c r="C10" s="5"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>227</v>
+      </c>
+      <c r="B11" s="11">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>193</v>
+      </c>
+      <c r="B12" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>195</v>
+      </c>
+      <c r="B13" t="s">
         <v>196</v>
       </c>
-      <c r="B8" s="5">
-        <v>439417.28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>197</v>
       </c>
-      <c r="B9" s="5">
-        <v>445489.88</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B14" t="s">
         <v>198</v>
       </c>
-      <c r="B10" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>200</v>
-      </c>
-      <c r="B11" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>202</v>
-      </c>
-      <c r="B12" t="s">
-        <v>203</v>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="D17" s="6"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="18" x14ac:dyDescent="0.25">
+      <c r="A24" s="9" t="s">
+        <v>243</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B12" xr:uid="{00000000-0009-0000-0000-000007000000}"/>
+  <autoFilter ref="A1:B14" xr:uid="{00000000-0009-0000-0000-000007000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6454,7 +6685,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -6463,24 +6694,24 @@
         <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B2" t="s">
         <v>13</v>
@@ -6501,12 +6732,12 @@
         <v>40</v>
       </c>
       <c r="H2" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
@@ -6527,12 +6758,12 @@
         <v>55</v>
       </c>
       <c r="H3" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
@@ -6553,18 +6784,18 @@
         <v>65</v>
       </c>
       <c r="H4" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D5">
         <v>85</v>
@@ -6579,18 +6810,18 @@
         <v>85</v>
       </c>
       <c r="H5" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D6">
         <v>95</v>
@@ -6605,18 +6836,18 @@
         <v>95</v>
       </c>
       <c r="H6" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B7" t="s">
         <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D7">
         <v>110</v>
@@ -6631,18 +6862,18 @@
         <v>110</v>
       </c>
       <c r="H7" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B8" t="s">
         <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D8">
         <v>125</v>
@@ -6657,18 +6888,18 @@
         <v>125</v>
       </c>
       <c r="H8" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B9" t="s">
         <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D9">
         <v>52</v>
@@ -6683,18 +6914,18 @@
         <v>52</v>
       </c>
       <c r="H9" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B10" t="s">
         <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D10">
         <v>75</v>
@@ -6709,18 +6940,18 @@
         <v>75</v>
       </c>
       <c r="H10" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B11" t="s">
         <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D11">
         <v>90</v>
@@ -6735,18 +6966,18 @@
         <v>90</v>
       </c>
       <c r="H11" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B12" t="s">
         <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D12">
         <v>105</v>
@@ -6761,18 +6992,18 @@
         <v>105</v>
       </c>
       <c r="H12" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B13" t="s">
         <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D13">
         <v>120</v>
@@ -6787,18 +7018,18 @@
         <v>120</v>
       </c>
       <c r="H13" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B14" t="s">
         <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D14">
         <v>55</v>
@@ -6813,18 +7044,18 @@
         <v>55</v>
       </c>
       <c r="H14" t="s">
-        <v>207</v>
+        <v>226</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B15" t="s">
         <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D15">
         <v>80</v>
@@ -6839,18 +7070,18 @@
         <v>80</v>
       </c>
       <c r="H15" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B16" t="s">
         <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D16">
         <v>100</v>
@@ -6865,18 +7096,18 @@
         <v>100</v>
       </c>
       <c r="H16" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B17" t="s">
         <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D17">
         <v>115</v>
@@ -6891,18 +7122,18 @@
         <v>115</v>
       </c>
       <c r="H17" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D18">
         <v>130</v>
@@ -6917,18 +7148,18 @@
         <v>130</v>
       </c>
       <c r="H18" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B19" t="s">
         <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D19">
         <v>50</v>
@@ -6943,18 +7174,18 @@
         <v>50</v>
       </c>
       <c r="H19" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B20" t="s">
         <v>36</v>
       </c>
       <c r="C20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D20">
         <v>72</v>
@@ -6969,18 +7200,18 @@
         <v>72</v>
       </c>
       <c r="H20" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B21" t="s">
         <v>37</v>
       </c>
       <c r="C21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D21">
         <v>88</v>
@@ -6995,7 +7226,7 @@
         <v>88</v>
       </c>
       <c r="H21" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
